--- a/demo/base_etp_demo.xlsx
+++ b/demo/base_etp_demo.xlsx
@@ -1995,4 +1995,237 @@
     <ignoredError numberStoredAsText="1" sqref="A1:S10"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F16B230D3CD39F4BAA3018F15263DE85" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5ae69f3139e7ef21b6cc103c990486d4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7fa62201-75e0-41c1-b197-21f4b9f9df04" xmlns:ns3="67d4690d-55be-4538-8d28-eed63c761cc5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7c50e1417aeafdb8d8b3d815e0063be9" ns2:_="" ns3:_="">
+    <xsd:import namespace="7fa62201-75e0-41c1-b197-21f4b9f9df04"/>
+    <xsd:import namespace="67d4690d-55be-4538-8d28-eed63c761cc5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7fa62201-75e0-41c1-b197-21f4b9f9df04" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="a8e8d813-e4e5-48d0-aeb8-e19ab3349c6b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="67d4690d-55be-4538-8d28-eed63c761cc5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a4b1418e-1abc-4596-86ca-d5530fa7bb6f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="67d4690d-55be-4538-8d28-eed63c761cc5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="67d4690d-55be-4538-8d28-eed63c761cc5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7fa62201-75e0-41c1-b197-21f4b9f9df04">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C45B2207-C37F-4636-B236-16C99BBC4B70}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3C43CA3-E570-4D07-BB64-4235076F738E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FAD21A0-FAB2-4AA0-889D-46CCC019583B}"/>
 </file>
--- a/demo/base_etp_demo.xlsx
+++ b/demo/base_etp_demo.xlsx
@@ -398,25 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P19"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="25.83203125" customWidth="1"/>
-    <col min="15" max="15" width="15.83203125" customWidth="1"/>
-    <col min="16" max="16" width="17.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:P13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,19 +452,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EMP001</v>
+        <v>M001</v>
       </c>
       <c r="B2" t="str">
-        <v>Marc Dupont</v>
+        <v>Lambert Emma</v>
       </c>
       <c r="C2" t="str">
-        <v>Production</v>
+        <v>Achats</v>
       </c>
       <c r="D2" t="str">
-        <v>Direction Industrielle</v>
+        <v>Supply Chain</v>
       </c>
       <c r="E2" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F2" t="str">
         <v>Europe</v>
@@ -491,16 +473,16 @@
         <v>France</v>
       </c>
       <c r="H2" t="str">
-        <v>Chef d'équipe</v>
+        <v>Procurement</v>
       </c>
       <c r="I2" t="str">
-        <v>Atelier A1</v>
+        <v>Achats directs</v>
       </c>
       <c r="J2" t="str">
-        <v>BU Industrie</v>
+        <v>Acme France</v>
       </c>
       <c r="K2" t="str">
-        <v>SAS</v>
+        <v>Acme France SAS</v>
       </c>
       <c r="L2" t="str">
         <v>Local</v>
@@ -509,30 +491,30 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>45000</v>
+        <v>58000</v>
       </c>
       <c r="O2" t="str">
-        <v>2018-03-12</v>
+        <v>2019-03-01</v>
       </c>
       <c r="P2" t="str">
-        <v>2035-06-30</v>
+        <v>2041-06-30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EMP002</v>
+        <v>M002</v>
       </c>
       <c r="B3" t="str">
-        <v>Léa Moreau</v>
+        <v>Garnier Louis</v>
       </c>
       <c r="C3" t="str">
-        <v>Production</v>
+        <v>Achats</v>
       </c>
       <c r="D3" t="str">
-        <v>Direction Industrielle</v>
+        <v>Supply Chain</v>
       </c>
       <c r="E3" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F3" t="str">
         <v>Europe</v>
@@ -541,16 +523,16 @@
         <v>France</v>
       </c>
       <c r="H3" t="str">
-        <v>Opérateur ligne</v>
+        <v>Procurement</v>
       </c>
       <c r="I3" t="str">
-        <v>Atelier A1</v>
+        <v>Achats directs</v>
       </c>
       <c r="J3" t="str">
-        <v>BU Industrie</v>
+        <v>Acme France</v>
       </c>
       <c r="K3" t="str">
-        <v>SAS</v>
+        <v>Acme France SAS</v>
       </c>
       <c r="L3" t="str">
         <v>Local</v>
@@ -559,30 +541,30 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>36000</v>
+        <v>52000</v>
       </c>
       <c r="O3" t="str">
-        <v>2020-09-01</v>
+        <v>2021-09-15</v>
       </c>
       <c r="P3" t="str">
-        <v>2042-11-15</v>
+        <v>2044-02-28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>EMP003</v>
+        <v>M003</v>
       </c>
       <c r="B4" t="str">
-        <v>Alex Roussel</v>
+        <v>Petit Camille</v>
       </c>
       <c r="C4" t="str">
-        <v>Commercial &amp; Marketing</v>
+        <v>Production</v>
       </c>
       <c r="D4" t="str">
-        <v>Direction Commerciale</v>
+        <v>Opérations</v>
       </c>
       <c r="E4" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F4" t="str">
         <v>Europe</v>
@@ -591,48 +573,48 @@
         <v>France</v>
       </c>
       <c r="H4" t="str">
-        <v>Account Manager</v>
+        <v>Operations</v>
       </c>
       <c r="I4" t="str">
-        <v>Grands comptes</v>
+        <v>Ligne B</v>
       </c>
       <c r="J4" t="str">
-        <v>BU Services</v>
+        <v>Acme France</v>
       </c>
       <c r="K4" t="str">
-        <v>SAS</v>
+        <v>Acme France SAS</v>
       </c>
       <c r="L4" t="str">
-        <v>Régional</v>
+        <v>Local</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4">
-        <v>58000</v>
+        <v>41000</v>
       </c>
       <c r="O4" t="str">
-        <v>2017-01-15</v>
+        <v>2017-01-10</v>
       </c>
       <c r="P4" t="str">
-        <v>2038-08-20</v>
+        <v>2038-11-30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EMP004</v>
+        <v>M004</v>
       </c>
       <c r="B5" t="str">
-        <v>Anaïs Petit</v>
+        <v>Roy Antoine</v>
       </c>
       <c r="C5" t="str">
-        <v>R&amp;D / Innovation</v>
+        <v>Production</v>
       </c>
       <c r="D5" t="str">
-        <v>Direction Innovation</v>
+        <v>Opérations</v>
       </c>
       <c r="E5" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F5" t="str">
         <v>Europe</v>
@@ -641,148 +623,148 @@
         <v>France</v>
       </c>
       <c r="H5" t="str">
-        <v>Ingénieur R&amp;D</v>
+        <v>Operations</v>
       </c>
       <c r="I5" t="str">
-        <v>Labo central</v>
+        <v>Ligne B</v>
       </c>
       <c r="J5" t="str">
-        <v>Corporate</v>
+        <v>Acme France</v>
       </c>
       <c r="K5" t="str">
-        <v>SAS</v>
+        <v>Acme France SAS</v>
       </c>
       <c r="L5" t="str">
-        <v>Régional</v>
+        <v>Local</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5">
-        <v>62000</v>
+        <v>43000</v>
       </c>
       <c r="O5" t="str">
-        <v>2019-06-01</v>
+        <v>2015-05-20</v>
       </c>
       <c r="P5" t="str">
-        <v>2045-03-10</v>
+        <v>2036-04-30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>EMP005</v>
+        <v>M005</v>
       </c>
       <c r="B6" t="str">
-        <v>Claire Bernard</v>
+        <v>Moreau Julie</v>
       </c>
       <c r="C6" t="str">
-        <v>Support (IT/Finance/HR)</v>
+        <v>Marketing</v>
       </c>
       <c r="D6" t="str">
-        <v>Direction Fonctions Support</v>
+        <v>Commercial</v>
       </c>
       <c r="E6" t="str">
-        <v>Nadia Benali</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="F6" t="str">
         <v>Europe</v>
       </c>
       <c r="G6" t="str">
-        <v>France</v>
+        <v>Germany</v>
       </c>
       <c r="H6" t="str">
-        <v>Analyste financier</v>
+        <v>Marketing</v>
       </c>
       <c r="I6" t="str">
-        <v>Contrôle de gestion</v>
+        <v>Marketing Central</v>
       </c>
       <c r="J6" t="str">
-        <v>Corporate</v>
+        <v>Acme Deutschland</v>
       </c>
       <c r="K6" t="str">
-        <v>SAS</v>
+        <v>Acme Deutschland GmbH</v>
       </c>
       <c r="L6" t="str">
-        <v>Local</v>
+        <v>Régional</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
       <c r="N6">
-        <v>52000</v>
+        <v>61000</v>
       </c>
       <c r="O6" t="str">
-        <v>2021-02-15</v>
+        <v>2020-02-01</v>
       </c>
       <c r="P6" t="str">
-        <v>2040-07-25</v>
+        <v>2043-01-31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>EMP006</v>
+        <v>M006</v>
       </c>
       <c r="B7" t="str">
-        <v>Jean Martin</v>
+        <v>Klein Hans</v>
       </c>
       <c r="C7" t="str">
-        <v>Supply Chain</v>
+        <v>Marketing</v>
       </c>
       <c r="D7" t="str">
-        <v>Direction Supply Chain</v>
+        <v>Commercial</v>
       </c>
       <c r="E7" t="str">
-        <v>Nadia Benali</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="F7" t="str">
         <v>Europe</v>
       </c>
       <c r="G7" t="str">
-        <v>France</v>
+        <v>Germany</v>
       </c>
       <c r="H7" t="str">
-        <v>Planificateur</v>
+        <v>Marketing</v>
       </c>
       <c r="I7" t="str">
-        <v>Planification</v>
+        <v>Marketing Central</v>
       </c>
       <c r="J7" t="str">
-        <v>BU Industrie</v>
+        <v>Acme Deutschland</v>
       </c>
       <c r="K7" t="str">
-        <v>SAS</v>
+        <v>Acme Deutschland GmbH</v>
       </c>
       <c r="L7" t="str">
-        <v>Local</v>
+        <v>Régional</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7">
-        <v>44000</v>
+        <v>63000</v>
       </c>
       <c r="O7" t="str">
-        <v>2016-11-01</v>
+        <v>2018-06-01</v>
       </c>
       <c r="P7" t="str">
-        <v>2033-09-30</v>
+        <v>2040-09-30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>EMP007</v>
+        <v>M007</v>
       </c>
       <c r="B8" t="str">
-        <v>Sophie Lambert</v>
+        <v>Fontaine Léa</v>
       </c>
       <c r="C8" t="str">
-        <v>Production</v>
+        <v>Finance</v>
       </c>
       <c r="D8" t="str">
-        <v>Direction Industrielle</v>
+        <v>Finance</v>
       </c>
       <c r="E8" t="str">
-        <v>Petra Schmidt</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="F8" t="str">
         <v>Europe</v>
@@ -791,16 +773,16 @@
         <v>Germany</v>
       </c>
       <c r="H8" t="str">
-        <v>Technicien maintenance</v>
+        <v>Finance</v>
       </c>
       <c r="I8" t="str">
-        <v>Atelier B2</v>
+        <v>Comptabilité</v>
       </c>
       <c r="J8" t="str">
-        <v>BU Industrie</v>
+        <v>Acme Deutschland</v>
       </c>
       <c r="K8" t="str">
-        <v>GmbH</v>
+        <v>Acme Deutschland GmbH</v>
       </c>
       <c r="L8" t="str">
         <v>Local</v>
@@ -809,48 +791,48 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>42000</v>
+        <v>55000</v>
       </c>
       <c r="O8" t="str">
-        <v>2019-04-10</v>
+        <v>2019-11-01</v>
       </c>
       <c r="P8" t="str">
-        <v>2039-01-15</v>
+        <v>2042-07-31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>EMP008</v>
+        <v>M008</v>
       </c>
       <c r="B9" t="str">
-        <v>Pierre Faure</v>
+        <v>Weber Paul</v>
       </c>
       <c r="C9" t="str">
-        <v>Commercial &amp; Marketing</v>
+        <v>Finance</v>
       </c>
       <c r="D9" t="str">
-        <v>Direction Commerciale</v>
+        <v>Finance</v>
       </c>
       <c r="E9" t="str">
-        <v>Nadia Benali</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="F9" t="str">
         <v>Europe</v>
       </c>
       <c r="G9" t="str">
-        <v>France</v>
+        <v>Germany</v>
       </c>
       <c r="H9" t="str">
-        <v>Business Developer</v>
+        <v>Finance</v>
       </c>
       <c r="I9" t="str">
-        <v>Nouveaux marchés</v>
+        <v>Comptabilité</v>
       </c>
       <c r="J9" t="str">
-        <v>BU Services</v>
+        <v>Acme Deutschland</v>
       </c>
       <c r="K9" t="str">
-        <v>SAS</v>
+        <v>Acme Deutschland GmbH</v>
       </c>
       <c r="L9" t="str">
         <v>Local</v>
@@ -859,98 +841,98 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>50000</v>
+        <v>56000</v>
       </c>
       <c r="O9" t="str">
-        <v>2022-07-01</v>
+        <v>2016-03-15</v>
       </c>
       <c r="P9" t="str">
-        <v>2043-05-20</v>
+        <v>2037-12-31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>EMP009</v>
+        <v>M009</v>
       </c>
       <c r="B10" t="str">
-        <v>Thomas Henry</v>
+        <v>Ruiz Sofia</v>
       </c>
       <c r="C10" t="str">
-        <v>Production</v>
+        <v>Ventes</v>
       </c>
       <c r="D10" t="str">
-        <v>Direction Industrielle</v>
+        <v>Commercial</v>
       </c>
       <c r="E10" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F10" t="str">
         <v>Europe</v>
       </c>
       <c r="G10" t="str">
-        <v>France</v>
+        <v>Spain</v>
       </c>
       <c r="H10" t="str">
-        <v>Ingénieur process</v>
+        <v>Sales</v>
       </c>
       <c r="I10" t="str">
-        <v>Atelier A2</v>
+        <v>Ventes Ibérie</v>
       </c>
       <c r="J10" t="str">
-        <v>BU Industrie</v>
+        <v>Acme Iberia</v>
       </c>
       <c r="K10" t="str">
-        <v>SAS</v>
+        <v>Acme Iberia SL</v>
       </c>
       <c r="L10" t="str">
-        <v>Régional</v>
+        <v>Local</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10">
-        <v>55000</v>
+        <v>48000</v>
       </c>
       <c r="O10" t="str">
-        <v>2015-08-20</v>
+        <v>2021-01-05</v>
       </c>
       <c r="P10" t="str">
-        <v>2036-12-31</v>
+        <v>2045-03-31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>EMP010</v>
+        <v>M010</v>
       </c>
       <c r="B11" t="str">
-        <v>Nicolas Chevalier</v>
+        <v>Diaz Mateo</v>
       </c>
       <c r="C11" t="str">
-        <v>Support (IT/Finance/HR)</v>
+        <v>Ventes</v>
       </c>
       <c r="D11" t="str">
-        <v>Direction Fonctions Support</v>
+        <v>Commercial</v>
       </c>
       <c r="E11" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F11" t="str">
         <v>Europe</v>
       </c>
       <c r="G11" t="str">
-        <v>France</v>
+        <v>Spain</v>
       </c>
       <c r="H11" t="str">
-        <v>Administrateur SI</v>
+        <v>Sales</v>
       </c>
       <c r="I11" t="str">
-        <v>Infrastructure</v>
+        <v>Ventes Ibérie</v>
       </c>
       <c r="J11" t="str">
-        <v>Corporate</v>
+        <v>Acme Iberia</v>
       </c>
       <c r="K11" t="str">
-        <v>SAS</v>
+        <v>Acme Iberia SL</v>
       </c>
       <c r="L11" t="str">
         <v>Local</v>
@@ -959,446 +941,125 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>48000</v>
+        <v>47000</v>
       </c>
       <c r="O11" t="str">
-        <v>2020-01-15</v>
+        <v>2022-04-01</v>
       </c>
       <c r="P11" t="str">
-        <v>2041-10-01</v>
+        <v>2047-08-31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>EMP011</v>
+        <v>M011</v>
       </c>
       <c r="B12" t="str">
-        <v>Lucas Masson</v>
+        <v>Cole Ryan</v>
       </c>
       <c r="C12" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D12" t="str">
         <v>Supply Chain</v>
       </c>
-      <c r="D12" t="str">
-        <v>Direction Supply Chain</v>
-      </c>
       <c r="E12" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F12" t="str">
-        <v>Europe</v>
+        <v>Americas</v>
       </c>
       <c r="G12" t="str">
-        <v>France</v>
+        <v>USA</v>
       </c>
       <c r="H12" t="str">
-        <v>Responsable entrepôt</v>
+        <v>Supply Chain</v>
       </c>
       <c r="I12" t="str">
-        <v>Entrepôt Lyon</v>
+        <v>Entrepôts</v>
       </c>
       <c r="J12" t="str">
-        <v>BU Industrie</v>
+        <v>Acme USA</v>
       </c>
       <c r="K12" t="str">
-        <v>SAS</v>
+        <v>Acme USA Inc.</v>
       </c>
       <c r="L12" t="str">
-        <v>Local</v>
+        <v>Régional</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12">
-        <v>46000</v>
+        <v>72000</v>
       </c>
       <c r="O12" t="str">
-        <v>2018-06-01</v>
+        <v>2014-09-01</v>
       </c>
       <c r="P12" t="str">
-        <v>2037-04-15</v>
+        <v>2039-05-31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>EMP012</v>
+        <v>M012</v>
       </c>
       <c r="B13" t="str">
-        <v>Emma Weber</v>
+        <v>Bennett Sarah</v>
       </c>
       <c r="C13" t="str">
-        <v>Production</v>
+        <v>Logistique</v>
       </c>
       <c r="D13" t="str">
-        <v>Direction Industrielle</v>
+        <v>Supply Chain</v>
       </c>
       <c r="E13" t="str">
-        <v>Petra Schmidt</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F13" t="str">
-        <v>Europe</v>
+        <v>Americas</v>
       </c>
       <c r="G13" t="str">
-        <v>Germany</v>
+        <v>USA</v>
       </c>
       <c r="H13" t="str">
-        <v>Responsable atelier</v>
+        <v>Supply Chain</v>
       </c>
       <c r="I13" t="str">
-        <v>Atelier B1</v>
+        <v>Entrepôts</v>
       </c>
       <c r="J13" t="str">
-        <v>BU Industrie</v>
+        <v>Acme USA</v>
       </c>
       <c r="K13" t="str">
-        <v>GmbH</v>
+        <v>Acme USA Inc.</v>
       </c>
       <c r="L13" t="str">
-        <v>Régional</v>
+        <v>Local</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13">
-        <v>56000</v>
+        <v>54000</v>
       </c>
       <c r="O13" t="str">
-        <v>2014-10-01</v>
+        <v>2019-07-01</v>
       </c>
       <c r="P13" t="str">
-        <v>2035-08-30</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>EMP013</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Hugo Schneider</v>
-      </c>
-      <c r="C14" t="str">
-        <v>R&amp;D / Innovation</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Direction Innovation</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Nadia Benali</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Europe</v>
-      </c>
-      <c r="G14" t="str">
-        <v>France</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Data Scientist</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Analytics</v>
-      </c>
-      <c r="J14" t="str">
-        <v>Corporate</v>
-      </c>
-      <c r="K14" t="str">
-        <v>SAS</v>
-      </c>
-      <c r="L14" t="str">
-        <v>Local</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>65000</v>
-      </c>
-      <c r="O14" t="str">
-        <v>2023-03-01</v>
-      </c>
-      <c r="P14" t="str">
-        <v>2050-02-28</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>EMP014</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Chloé Rossi</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Commercial &amp; Marketing</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Direction Commerciale</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Nadia Benali</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Europe</v>
-      </c>
-      <c r="G15" t="str">
-        <v>France</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Chargé de marketing</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Digital marketing</v>
-      </c>
-      <c r="J15" t="str">
-        <v>BU Services</v>
-      </c>
-      <c r="K15" t="str">
-        <v>SAS</v>
-      </c>
-      <c r="L15" t="str">
-        <v>Local</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>47000</v>
-      </c>
-      <c r="O15" t="str">
-        <v>2021-09-15</v>
-      </c>
-      <c r="P15" t="str">
-        <v>2044-06-10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>EMP015</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Louis Ferrari</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Supply Chain</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Direction Supply Chain</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Nadia Benali</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Europe</v>
-      </c>
-      <c r="G16" t="str">
-        <v>France</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Coordinateur logistique</v>
-      </c>
-      <c r="I16" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="J16" t="str">
-        <v>BU Industrie</v>
-      </c>
-      <c r="K16" t="str">
-        <v>SAS</v>
-      </c>
-      <c r="L16" t="str">
-        <v>Local</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>40000</v>
-      </c>
-      <c r="O16" t="str">
-        <v>2022-04-01</v>
-      </c>
-      <c r="P16" t="str">
-        <v>2046-07-20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>EMP016</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Camille Garcia</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Production</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Direction Industrielle</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Nadia Benali</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Europe</v>
-      </c>
-      <c r="G17" t="str">
-        <v>France</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Opérateur ligne</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Atelier A3</v>
-      </c>
-      <c r="J17" t="str">
-        <v>BU Industrie</v>
-      </c>
-      <c r="K17" t="str">
-        <v>SAS</v>
-      </c>
-      <c r="L17" t="str">
-        <v>Local</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>35000</v>
-      </c>
-      <c r="O17" t="str">
-        <v>2023-01-10</v>
-      </c>
-      <c r="P17" t="str">
-        <v>2052-12-15</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>EMP017</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Nathan Lopez</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Support (IT/Finance/HR)</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Direction Fonctions Support</v>
-      </c>
-      <c r="E18" t="str">
-        <v>Petra Schmidt</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Europe</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Gestionnaire paie</v>
-      </c>
-      <c r="I18" t="str">
-        <v>RH Allemagne</v>
-      </c>
-      <c r="J18" t="str">
-        <v>Corporate</v>
-      </c>
-      <c r="K18" t="str">
-        <v>GmbH</v>
-      </c>
-      <c r="L18" t="str">
-        <v>Local</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <v>43000</v>
-      </c>
-      <c r="O18" t="str">
-        <v>2019-11-01</v>
-      </c>
-      <c r="P18" t="str">
-        <v>2038-03-25</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>EMP018</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Sarah Smith</v>
-      </c>
-      <c r="C19" t="str">
-        <v>R&amp;D / Innovation</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Direction Innovation</v>
-      </c>
-      <c r="E19" t="str">
-        <v>Nadia Benali</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Europe</v>
-      </c>
-      <c r="G19" t="str">
-        <v>France</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Chef de projet innovation</v>
-      </c>
-      <c r="I19" t="str">
-        <v>InnovationLab</v>
-      </c>
-      <c r="J19" t="str">
-        <v>Corporate</v>
-      </c>
-      <c r="K19" t="str">
-        <v>SAS</v>
-      </c>
-      <c r="L19" t="str">
-        <v>Régional</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>60000</v>
-      </c>
-      <c r="O19" t="str">
-        <v>2018-07-15</v>
-      </c>
-      <c r="P19" t="str">
-        <v>2040-09-30</v>
+        <v>2044-10-31</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S10"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="23.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" customWidth="1"/>
-    <col min="15" max="15" width="14.83203125" customWidth="1"/>
-    <col min="16" max="16" width="31.83203125" customWidth="1"/>
-    <col min="17" max="17" width="15.83203125" customWidth="1"/>
-    <col min="18" max="18" width="18.83203125" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:S7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1461,155 +1122,155 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>MV001</v>
+        <v>MV-001</v>
       </c>
       <c r="B2" t="str">
-        <v>EMP002</v>
+        <v>M002</v>
       </c>
       <c r="C2" t="str">
-        <v>Léa Moreau</v>
+        <v>Garnier Louis</v>
       </c>
       <c r="D2" t="str">
-        <v>Redéploiement</v>
+        <v>Suppression</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>Production</v>
+        <v>Achats</v>
       </c>
       <c r="G2" t="str">
-        <v>Supply Chain</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v>France</v>
       </c>
       <c r="I2" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="J2" t="str">
         <v>AC-001</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-07-01</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-04-15</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>Réalisé</v>
+        <v>Planifié</v>
       </c>
       <c r="N2" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="O2" t="str">
         <v>Non</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>-52000</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="R2">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="S2" t="str">
-        <v>Transfert vers planification supply chain après formation</v>
+        <v>Poste supprimé suite au regroupement fournisseurs.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MV002</v>
+        <v>MV-002</v>
       </c>
       <c r="B3" t="str">
-        <v>EMP008</v>
+        <v>M004</v>
       </c>
       <c r="C3" t="str">
-        <v>Pierre Faure</v>
+        <v>Roy Antoine</v>
       </c>
       <c r="D3" t="str">
-        <v>Suppression</v>
+        <v>Redéploiement</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>Commercial &amp; Marketing</v>
+        <v>Production</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>Maintenance</v>
       </c>
       <c r="H3" t="str">
         <v>France</v>
       </c>
       <c r="I3" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="J3" t="str">
-        <v>AC-004</v>
+        <v>AC-002</v>
       </c>
       <c r="K3" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>2026-06-01</v>
       </c>
       <c r="M3" t="str">
-        <v>Planifié</v>
+        <v>Réalisé</v>
       </c>
       <c r="N3" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="O3" t="str">
         <v>Non</v>
       </c>
       <c r="P3">
-        <v>-50000</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>25000</v>
+        <v>2000</v>
       </c>
       <c r="S3" t="str">
-        <v>Poste supprimé dans le cadre de la fusion des équipes SC</v>
+        <v>Reclassé sur l'équipe maintenance préventive.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>MV003</v>
+        <v>MV-003</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>M006</v>
       </c>
       <c r="C4" t="str">
-        <v>Data Analyst Senior</v>
+        <v>Klein Hans</v>
       </c>
       <c r="D4" t="str">
-        <v>Recrutement</v>
+        <v>Reconversion</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>Support (IT/Finance/HR)</v>
+        <v>Marketing</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>Marketing Central</v>
       </c>
       <c r="H4" t="str">
-        <v>France</v>
+        <v>Germany</v>
       </c>
       <c r="I4" t="str">
-        <v>Nadia Benali</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="J4" t="str">
-        <v>AC-003</v>
+        <v>AC-004</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -1621,89 +1282,89 @@
         <v>Non</v>
       </c>
       <c r="O4" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="P4">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="S4" t="str">
-        <v>Profil nécessaire pour piloter l'automatisation RPA</v>
+        <v>Formation de reconversion suite à la fusion des équipes.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>MV004</v>
+        <v>MV-004</v>
       </c>
       <c r="B5" t="str">
-        <v>EMP015</v>
+        <v>M008</v>
       </c>
       <c r="C5" t="str">
-        <v>Louis Ferrari</v>
+        <v>Weber Paul</v>
       </c>
       <c r="D5" t="str">
-        <v>Reconversion</v>
+        <v>Suppression</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>Supply Chain</v>
+        <v>Finance</v>
       </c>
       <c r="G5" t="str">
-        <v>Production</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>France</v>
+        <v>Germany</v>
       </c>
       <c r="I5" t="str">
-        <v>Nadia Benali</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="J5" t="str">
-        <v>AC-006</v>
+        <v>AC-003</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-07-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>En cours</v>
+        <v>Planifié</v>
       </c>
       <c r="N5" t="str">
         <v>Non</v>
       </c>
       <c r="O5" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="P5">
-        <v>-4000</v>
+        <v>-56000</v>
       </c>
       <c r="Q5">
-        <v>4000</v>
+        <v>56000</v>
       </c>
       <c r="R5">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="S5" t="str">
-        <v>Reconversion opérateur → coordinateur atelier Rotterdam</v>
+        <v>Automatisation du back-office comptable.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>MV005</v>
+        <v>MV-005</v>
       </c>
       <c r="B6" t="str">
-        <v>EMP007</v>
+        <v>M012</v>
       </c>
       <c r="C6" t="str">
-        <v>Sophie Lambert</v>
+        <v>Bennett Sarah</v>
       </c>
       <c r="D6" t="str">
         <v>Redéploiement</v>
@@ -1712,31 +1373,31 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>Production</v>
+        <v>Logistique</v>
       </c>
       <c r="G6" t="str">
-        <v>R&amp;D / Innovation</v>
+        <v>Entrepôts</v>
       </c>
       <c r="H6" t="str">
-        <v>Germany</v>
+        <v>USA</v>
       </c>
       <c r="I6" t="str">
-        <v>Petra Schmidt</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="J6" t="str">
-        <v>AC-002</v>
+        <v>AC-006</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-05-15</v>
+        <v>2026-09-01</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-05-15</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>Réalisé</v>
+        <v>Planifié</v>
       </c>
       <c r="N6" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="O6" t="str">
         <v>Non</v>
@@ -1748,21 +1409,21 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="S6" t="str">
-        <v>Affectation au pôle maintenance prédictive</v>
+        <v>Réaffectée sur le site consolidé.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>MV006</v>
+        <v>MV-006</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>Responsable Qualité</v>
+        <v>Ingénieur Qualité (à recruter)</v>
       </c>
       <c r="D7" t="str">
         <v>Recrutement</v>
@@ -1777,16 +1438,16 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Belgium</v>
+        <v>France</v>
       </c>
       <c r="I7" t="str">
-        <v>Nadia Benali</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="J7" t="str">
         <v>AC-007</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-01</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -1801,431 +1462,21 @@
         <v>Non</v>
       </c>
       <c r="P7">
-        <v>58000</v>
+        <v>45000</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>22000</v>
+        <v>4000</v>
       </c>
       <c r="S7" t="str">
-        <v>Recrutement pour piloter le programme Six Sigma Belgique</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>MV007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>EMP016</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Camille Garcia</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Suppression</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Production</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v>France</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Nadia Benali</v>
-      </c>
-      <c r="J8" t="str">
-        <v>AC-002</v>
-      </c>
-      <c r="K8" t="str">
-        <v>2026-08-01</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v>Planifié</v>
-      </c>
-      <c r="N8" t="str">
-        <v>Non</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Non</v>
-      </c>
-      <c r="P8">
-        <v>-35000</v>
-      </c>
-      <c r="Q8">
-        <v>35000</v>
-      </c>
-      <c r="R8">
-        <v>18000</v>
-      </c>
-      <c r="S8" t="str">
-        <v>Poste rendu obsolète par l'automatisation de la ligne A3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>MV008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>EMP012</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Emma Weber</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Reconversion</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Production</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Support (IT/Finance/HR)</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Petra Schmidt</v>
-      </c>
-      <c r="J9" t="str">
-        <v>AC-003</v>
-      </c>
-      <c r="K9" t="str">
-        <v>2026-09-01</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v>Planifié</v>
-      </c>
-      <c r="N9" t="str">
-        <v>Non</v>
-      </c>
-      <c r="O9" t="str">
-        <v>Non</v>
-      </c>
-      <c r="P9">
-        <v>-5600</v>
-      </c>
-      <c r="Q9">
-        <v>5600</v>
-      </c>
-      <c r="R9">
-        <v>15000</v>
-      </c>
-      <c r="S9" t="str">
-        <v>Reconversion vers chef de projet digital manufacturing</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>MV009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>EMP009</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Thomas Henry</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Redéploiement</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Production</v>
-      </c>
-      <c r="G10" t="str">
-        <v>R&amp;D / Innovation</v>
-      </c>
-      <c r="H10" t="str">
-        <v>France</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Nadia Benali</v>
-      </c>
-      <c r="J10" t="str">
-        <v>AC-003</v>
-      </c>
-      <c r="K10" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="L10" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="M10" t="str">
-        <v>Réalisé</v>
-      </c>
-      <c r="N10" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="O10" t="str">
-        <v>Non</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>8000</v>
-      </c>
-      <c r="S10" t="str">
-        <v>Expert process transféré pour accompagner l'automatisation</v>
+        <v>Recrutement lié au programme qualité production.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F16B230D3CD39F4BAA3018F15263DE85" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5ae69f3139e7ef21b6cc103c990486d4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7fa62201-75e0-41c1-b197-21f4b9f9df04" xmlns:ns3="67d4690d-55be-4538-8d28-eed63c761cc5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7c50e1417aeafdb8d8b3d815e0063be9" ns2:_="" ns3:_="">
-    <xsd:import namespace="7fa62201-75e0-41c1-b197-21f4b9f9df04"/>
-    <xsd:import namespace="67d4690d-55be-4538-8d28-eed63c761cc5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7fa62201-75e0-41c1-b197-21f4b9f9df04" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="a8e8d813-e4e5-48d0-aeb8-e19ab3349c6b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="67d4690d-55be-4538-8d28-eed63c761cc5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a4b1418e-1abc-4596-86ca-d5530fa7bb6f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="67d4690d-55be-4538-8d28-eed63c761cc5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="67d4690d-55be-4538-8d28-eed63c761cc5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7fa62201-75e0-41c1-b197-21f4b9f9df04">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C45B2207-C37F-4636-B236-16C99BBC4B70}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3C43CA3-E570-4D07-BB64-4235076F738E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FAD21A0-FAB2-4AA0-889D-46CCC019583B}"/>
 </file>
--- a/demo/base_etp_demo.xlsx
+++ b/demo/base_etp_demo.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -491,13 +491,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>58000</v>
+        <v>38000</v>
       </c>
       <c r="O2" t="str">
-        <v>2019-03-01</v>
+        <v>2012-01-01</v>
       </c>
       <c r="P2" t="str">
-        <v>2041-06-30</v>
+        <v>2033-06-28</v>
       </c>
     </row>
     <row r="3">
@@ -508,10 +508,10 @@
         <v>Garnier Louis</v>
       </c>
       <c r="C3" t="str">
-        <v>Achats</v>
+        <v>Production</v>
       </c>
       <c r="D3" t="str">
-        <v>Supply Chain</v>
+        <v>Opérations</v>
       </c>
       <c r="E3" t="str">
         <v>Sophie Dubois</v>
@@ -520,19 +520,19 @@
         <v>Europe</v>
       </c>
       <c r="G3" t="str">
-        <v>France</v>
+        <v>Germany</v>
       </c>
       <c r="H3" t="str">
-        <v>Procurement</v>
+        <v>Operations</v>
       </c>
       <c r="I3" t="str">
-        <v>Achats directs</v>
+        <v>Ligne de production</v>
       </c>
       <c r="J3" t="str">
-        <v>Acme France</v>
+        <v>Acme Deutschland</v>
       </c>
       <c r="K3" t="str">
-        <v>Acme France SAS</v>
+        <v>Acme Deutschland GmbH</v>
       </c>
       <c r="L3" t="str">
         <v>Local</v>
@@ -541,13 +541,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>52000</v>
+        <v>38733</v>
       </c>
       <c r="O3" t="str">
-        <v>2021-09-15</v>
+        <v>2013-02-02</v>
       </c>
       <c r="P3" t="str">
-        <v>2044-02-28</v>
+        <v>2035-07-28</v>
       </c>
     </row>
     <row r="4">
@@ -558,31 +558,31 @@
         <v>Petit Camille</v>
       </c>
       <c r="C4" t="str">
-        <v>Production</v>
+        <v>Marketing</v>
       </c>
       <c r="D4" t="str">
-        <v>Opérations</v>
+        <v>Commercial</v>
       </c>
       <c r="E4" t="str">
-        <v>Sophie Dubois</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="F4" t="str">
         <v>Europe</v>
       </c>
       <c r="G4" t="str">
-        <v>France</v>
+        <v>Spain</v>
       </c>
       <c r="H4" t="str">
-        <v>Operations</v>
+        <v>Marketing</v>
       </c>
       <c r="I4" t="str">
-        <v>Ligne B</v>
+        <v>Marketing Central</v>
       </c>
       <c r="J4" t="str">
-        <v>Acme France</v>
+        <v>Acme Iberia</v>
       </c>
       <c r="K4" t="str">
-        <v>Acme France SAS</v>
+        <v>Acme Iberia SL</v>
       </c>
       <c r="L4" t="str">
         <v>Local</v>
@@ -591,13 +591,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>41000</v>
+        <v>39466</v>
       </c>
       <c r="O4" t="str">
-        <v>2017-01-10</v>
+        <v>2014-03-03</v>
       </c>
       <c r="P4" t="str">
-        <v>2038-11-30</v>
+        <v>2037-08-28</v>
       </c>
     </row>
     <row r="5">
@@ -608,46 +608,46 @@
         <v>Roy Antoine</v>
       </c>
       <c r="C5" t="str">
-        <v>Production</v>
+        <v>Finance</v>
       </c>
       <c r="D5" t="str">
-        <v>Opérations</v>
+        <v>Finance</v>
       </c>
       <c r="E5" t="str">
-        <v>Sophie Dubois</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="F5" t="str">
-        <v>Europe</v>
+        <v>Americas</v>
       </c>
       <c r="G5" t="str">
-        <v>France</v>
+        <v>USA</v>
       </c>
       <c r="H5" t="str">
-        <v>Operations</v>
+        <v>Finance</v>
       </c>
       <c r="I5" t="str">
-        <v>Ligne B</v>
+        <v>Comptabilité</v>
       </c>
       <c r="J5" t="str">
-        <v>Acme France</v>
+        <v>Acme USA</v>
       </c>
       <c r="K5" t="str">
-        <v>Acme France SAS</v>
+        <v>Acme USA Inc.</v>
       </c>
       <c r="L5" t="str">
-        <v>Local</v>
+        <v>Régional</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5">
-        <v>43000</v>
+        <v>40199</v>
       </c>
       <c r="O5" t="str">
-        <v>2015-05-20</v>
+        <v>2015-04-04</v>
       </c>
       <c r="P5" t="str">
-        <v>2036-04-30</v>
+        <v>2039-09-28</v>
       </c>
     </row>
     <row r="6">
@@ -658,46 +658,46 @@
         <v>Moreau Julie</v>
       </c>
       <c r="C6" t="str">
-        <v>Marketing</v>
+        <v>Ventes</v>
       </c>
       <c r="D6" t="str">
         <v>Commercial</v>
       </c>
       <c r="E6" t="str">
-        <v>Claire Moreau</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F6" t="str">
         <v>Europe</v>
       </c>
       <c r="G6" t="str">
-        <v>Germany</v>
+        <v>France</v>
       </c>
       <c r="H6" t="str">
-        <v>Marketing</v>
+        <v>Sales</v>
       </c>
       <c r="I6" t="str">
-        <v>Marketing Central</v>
+        <v>Ventes terrain</v>
       </c>
       <c r="J6" t="str">
-        <v>Acme Deutschland</v>
+        <v>Acme France</v>
       </c>
       <c r="K6" t="str">
-        <v>Acme Deutschland GmbH</v>
+        <v>Acme France SAS</v>
       </c>
       <c r="L6" t="str">
-        <v>Régional</v>
+        <v>Global</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
       <c r="N6">
-        <v>61000</v>
+        <v>40932</v>
       </c>
       <c r="O6" t="str">
-        <v>2020-02-01</v>
+        <v>2016-05-05</v>
       </c>
       <c r="P6" t="str">
-        <v>2043-01-31</v>
+        <v>2041-10-28</v>
       </c>
     </row>
     <row r="7">
@@ -708,13 +708,13 @@
         <v>Klein Hans</v>
       </c>
       <c r="C7" t="str">
-        <v>Marketing</v>
+        <v>Logistique</v>
       </c>
       <c r="D7" t="str">
-        <v>Commercial</v>
+        <v>Supply Chain</v>
       </c>
       <c r="E7" t="str">
-        <v>Claire Moreau</v>
+        <v>Sophie Dubois</v>
       </c>
       <c r="F7" t="str">
         <v>Europe</v>
@@ -723,10 +723,10 @@
         <v>Germany</v>
       </c>
       <c r="H7" t="str">
-        <v>Marketing</v>
+        <v>Supply Chain</v>
       </c>
       <c r="I7" t="str">
-        <v>Marketing Central</v>
+        <v>Entrepôts</v>
       </c>
       <c r="J7" t="str">
         <v>Acme Deutschland</v>
@@ -735,19 +735,19 @@
         <v>Acme Deutschland GmbH</v>
       </c>
       <c r="L7" t="str">
-        <v>Régional</v>
+        <v>Local</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7">
-        <v>63000</v>
+        <v>41665</v>
       </c>
       <c r="O7" t="str">
-        <v>2018-06-01</v>
+        <v>2017-06-06</v>
       </c>
       <c r="P7" t="str">
-        <v>2040-09-30</v>
+        <v>2043-11-28</v>
       </c>
     </row>
     <row r="8">
@@ -758,10 +758,10 @@
         <v>Fontaine Léa</v>
       </c>
       <c r="C8" t="str">
-        <v>Finance</v>
+        <v>IT</v>
       </c>
       <c r="D8" t="str">
-        <v>Finance</v>
+        <v>IT</v>
       </c>
       <c r="E8" t="str">
         <v>Claire Moreau</v>
@@ -770,19 +770,19 @@
         <v>Europe</v>
       </c>
       <c r="G8" t="str">
-        <v>Germany</v>
+        <v>Spain</v>
       </c>
       <c r="H8" t="str">
-        <v>Finance</v>
+        <v>IT</v>
       </c>
       <c r="I8" t="str">
-        <v>Comptabilité</v>
+        <v>Support SI</v>
       </c>
       <c r="J8" t="str">
-        <v>Acme Deutschland</v>
+        <v>Acme Iberia</v>
       </c>
       <c r="K8" t="str">
-        <v>Acme Deutschland GmbH</v>
+        <v>Acme Iberia SL</v>
       </c>
       <c r="L8" t="str">
         <v>Local</v>
@@ -791,13 +791,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>55000</v>
+        <v>42398</v>
       </c>
       <c r="O8" t="str">
-        <v>2019-11-01</v>
+        <v>2018-07-07</v>
       </c>
       <c r="P8" t="str">
-        <v>2042-07-31</v>
+        <v>2045-12-28</v>
       </c>
     </row>
     <row r="9">
@@ -808,31 +808,31 @@
         <v>Weber Paul</v>
       </c>
       <c r="C9" t="str">
-        <v>Finance</v>
+        <v>RH</v>
       </c>
       <c r="D9" t="str">
-        <v>Finance</v>
+        <v>RH</v>
       </c>
       <c r="E9" t="str">
         <v>Claire Moreau</v>
       </c>
       <c r="F9" t="str">
-        <v>Europe</v>
+        <v>Americas</v>
       </c>
       <c r="G9" t="str">
-        <v>Germany</v>
+        <v>USA</v>
       </c>
       <c r="H9" t="str">
-        <v>Finance</v>
+        <v>HR</v>
       </c>
       <c r="I9" t="str">
-        <v>Comptabilité</v>
+        <v>RH Généraliste</v>
       </c>
       <c r="J9" t="str">
-        <v>Acme Deutschland</v>
+        <v>Acme USA</v>
       </c>
       <c r="K9" t="str">
-        <v>Acme Deutschland GmbH</v>
+        <v>Acme USA Inc.</v>
       </c>
       <c r="L9" t="str">
         <v>Local</v>
@@ -841,13 +841,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>56000</v>
+        <v>43131</v>
       </c>
       <c r="O9" t="str">
-        <v>2016-03-15</v>
+        <v>2019-08-08</v>
       </c>
       <c r="P9" t="str">
-        <v>2037-12-31</v>
+        <v>2047-01-28</v>
       </c>
     </row>
     <row r="10">
@@ -858,10 +858,10 @@
         <v>Ruiz Sofia</v>
       </c>
       <c r="C10" t="str">
-        <v>Ventes</v>
+        <v>Achats</v>
       </c>
       <c r="D10" t="str">
-        <v>Commercial</v>
+        <v>Supply Chain</v>
       </c>
       <c r="E10" t="str">
         <v>Sophie Dubois</v>
@@ -870,34 +870,34 @@
         <v>Europe</v>
       </c>
       <c r="G10" t="str">
-        <v>Spain</v>
+        <v>France</v>
       </c>
       <c r="H10" t="str">
-        <v>Sales</v>
+        <v>Procurement</v>
       </c>
       <c r="I10" t="str">
-        <v>Ventes Ibérie</v>
+        <v>Achats directs</v>
       </c>
       <c r="J10" t="str">
-        <v>Acme Iberia</v>
+        <v>Acme France</v>
       </c>
       <c r="K10" t="str">
-        <v>Acme Iberia SL</v>
+        <v>Acme France SAS</v>
       </c>
       <c r="L10" t="str">
-        <v>Local</v>
+        <v>Régional</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10">
-        <v>48000</v>
+        <v>43864</v>
       </c>
       <c r="O10" t="str">
-        <v>2021-01-05</v>
+        <v>2020-09-09</v>
       </c>
       <c r="P10" t="str">
-        <v>2045-03-31</v>
+        <v>2049-02-28</v>
       </c>
     </row>
     <row r="11">
@@ -908,10 +908,10 @@
         <v>Diaz Mateo</v>
       </c>
       <c r="C11" t="str">
-        <v>Ventes</v>
+        <v>Production</v>
       </c>
       <c r="D11" t="str">
-        <v>Commercial</v>
+        <v>Opérations</v>
       </c>
       <c r="E11" t="str">
         <v>Sophie Dubois</v>
@@ -920,34 +920,34 @@
         <v>Europe</v>
       </c>
       <c r="G11" t="str">
-        <v>Spain</v>
+        <v>Germany</v>
       </c>
       <c r="H11" t="str">
-        <v>Sales</v>
+        <v>Operations</v>
       </c>
       <c r="I11" t="str">
-        <v>Ventes Ibérie</v>
+        <v>Ligne de production</v>
       </c>
       <c r="J11" t="str">
-        <v>Acme Iberia</v>
+        <v>Acme Deutschland</v>
       </c>
       <c r="K11" t="str">
-        <v>Acme Iberia SL</v>
+        <v>Acme Deutschland GmbH</v>
       </c>
       <c r="L11" t="str">
-        <v>Local</v>
+        <v>Global</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11">
-        <v>47000</v>
+        <v>44597</v>
       </c>
       <c r="O11" t="str">
-        <v>2022-04-01</v>
+        <v>2021-10-10</v>
       </c>
       <c r="P11" t="str">
-        <v>2047-08-31</v>
+        <v>2051-03-28</v>
       </c>
     </row>
     <row r="12">
@@ -958,46 +958,46 @@
         <v>Cole Ryan</v>
       </c>
       <c r="C12" t="str">
-        <v>Logistique</v>
+        <v>Marketing</v>
       </c>
       <c r="D12" t="str">
-        <v>Supply Chain</v>
+        <v>Commercial</v>
       </c>
       <c r="E12" t="str">
-        <v>Sophie Dubois</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="F12" t="str">
-        <v>Americas</v>
+        <v>Europe</v>
       </c>
       <c r="G12" t="str">
-        <v>USA</v>
+        <v>Spain</v>
       </c>
       <c r="H12" t="str">
-        <v>Supply Chain</v>
+        <v>Marketing</v>
       </c>
       <c r="I12" t="str">
-        <v>Entrepôts</v>
+        <v>Marketing Central</v>
       </c>
       <c r="J12" t="str">
-        <v>Acme USA</v>
+        <v>Acme Iberia</v>
       </c>
       <c r="K12" t="str">
-        <v>Acme USA Inc.</v>
+        <v>Acme Iberia SL</v>
       </c>
       <c r="L12" t="str">
-        <v>Régional</v>
+        <v>Local</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12">
-        <v>72000</v>
+        <v>45330</v>
       </c>
       <c r="O12" t="str">
-        <v>2014-09-01</v>
+        <v>2022-11-11</v>
       </c>
       <c r="P12" t="str">
-        <v>2039-05-31</v>
+        <v>2053-04-28</v>
       </c>
     </row>
     <row r="13">
@@ -1008,13 +1008,13 @@
         <v>Bennett Sarah</v>
       </c>
       <c r="C13" t="str">
-        <v>Logistique</v>
+        <v>Finance</v>
       </c>
       <c r="D13" t="str">
-        <v>Supply Chain</v>
+        <v>Finance</v>
       </c>
       <c r="E13" t="str">
-        <v>Sophie Dubois</v>
+        <v>Claire Moreau</v>
       </c>
       <c r="F13" t="str">
         <v>Americas</v>
@@ -1023,10 +1023,10 @@
         <v>USA</v>
       </c>
       <c r="H13" t="str">
-        <v>Supply Chain</v>
+        <v>Finance</v>
       </c>
       <c r="I13" t="str">
-        <v>Entrepôts</v>
+        <v>Comptabilité</v>
       </c>
       <c r="J13" t="str">
         <v>Acme USA</v>
@@ -1041,25 +1041,4425 @@
         <v>1</v>
       </c>
       <c r="N13">
-        <v>54000</v>
+        <v>46063</v>
       </c>
       <c r="O13" t="str">
-        <v>2019-07-01</v>
+        <v>2023-12-12</v>
       </c>
       <c r="P13" t="str">
-        <v>2044-10-31</v>
+        <v>2055-05-28</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>M013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Girard Nadia</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G14" t="str">
+        <v>France</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>46796</v>
+      </c>
+      <c r="O14" t="str">
+        <v>2024-01-13</v>
+      </c>
+      <c r="P14" t="str">
+        <v>2057-06-28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>M014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Bernard Marc</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>47529</v>
+      </c>
+      <c r="O15" t="str">
+        <v>2012-02-14</v>
+      </c>
+      <c r="P15" t="str">
+        <v>2046-07-28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>M015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Alvarez Elena</v>
+      </c>
+      <c r="C16" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D16" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H16" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>48262</v>
+      </c>
+      <c r="O16" t="str">
+        <v>2013-03-15</v>
+      </c>
+      <c r="P16" t="str">
+        <v>2048-08-28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>M016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Dahl Thomas</v>
+      </c>
+      <c r="C17" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D17" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G17" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H17" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I17" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>48995</v>
+      </c>
+      <c r="O17" t="str">
+        <v>2014-04-16</v>
+      </c>
+      <c r="P17" t="str">
+        <v>2035-09-28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>M017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Vasseur Claire</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G18" t="str">
+        <v>France</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>49728</v>
+      </c>
+      <c r="O18" t="str">
+        <v>2015-05-17</v>
+      </c>
+      <c r="P18" t="str">
+        <v>2037-10-28</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>M018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Blanc Julien</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>50461</v>
+      </c>
+      <c r="O19" t="str">
+        <v>2016-06-18</v>
+      </c>
+      <c r="P19" t="str">
+        <v>2039-11-28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>M019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Nystrom Henrik</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>51194</v>
+      </c>
+      <c r="O20" t="str">
+        <v>2017-07-19</v>
+      </c>
+      <c r="P20" t="str">
+        <v>2041-12-28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>M020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Keller Ines</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G21" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>51927</v>
+      </c>
+      <c r="O21" t="str">
+        <v>2018-08-20</v>
+      </c>
+      <c r="P21" t="str">
+        <v>2043-01-28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>M021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Garnier Emma</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G22" t="str">
+        <v>France</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>52660</v>
+      </c>
+      <c r="O22" t="str">
+        <v>2019-09-21</v>
+      </c>
+      <c r="P22" t="str">
+        <v>2045-02-28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>M022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Petit Louis</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>53393</v>
+      </c>
+      <c r="O23" t="str">
+        <v>2020-10-22</v>
+      </c>
+      <c r="P23" t="str">
+        <v>2047-03-28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>M023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Roy Camille</v>
+      </c>
+      <c r="C24" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D24" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H24" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>54126</v>
+      </c>
+      <c r="O24" t="str">
+        <v>2021-11-23</v>
+      </c>
+      <c r="P24" t="str">
+        <v>2049-04-28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>M024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Moreau Antoine</v>
+      </c>
+      <c r="C25" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D25" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G25" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H25" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I25" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>54859</v>
+      </c>
+      <c r="O25" t="str">
+        <v>2022-12-24</v>
+      </c>
+      <c r="P25" t="str">
+        <v>2051-05-28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>M025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Klein Julie</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G26" t="str">
+        <v>France</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>55592</v>
+      </c>
+      <c r="O26" t="str">
+        <v>2023-01-25</v>
+      </c>
+      <c r="P26" t="str">
+        <v>2053-06-28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>M026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Fontaine Hans</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>56325</v>
+      </c>
+      <c r="O27" t="str">
+        <v>2024-02-26</v>
+      </c>
+      <c r="P27" t="str">
+        <v>2055-07-28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>M027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Weber Léa</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>57058</v>
+      </c>
+      <c r="O28" t="str">
+        <v>2012-03-27</v>
+      </c>
+      <c r="P28" t="str">
+        <v>2044-08-28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>M028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Ruiz Paul</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G29" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>57791</v>
+      </c>
+      <c r="O29" t="str">
+        <v>2013-04-01</v>
+      </c>
+      <c r="P29" t="str">
+        <v>2046-09-28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>M029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Diaz Sofia</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G30" t="str">
+        <v>France</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>58524</v>
+      </c>
+      <c r="O30" t="str">
+        <v>2014-05-02</v>
+      </c>
+      <c r="P30" t="str">
+        <v>2048-10-28</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>M030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Cole Mateo</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>59257</v>
+      </c>
+      <c r="O31" t="str">
+        <v>2015-06-03</v>
+      </c>
+      <c r="P31" t="str">
+        <v>2050-11-28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>M031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Bennett Ryan</v>
+      </c>
+      <c r="C32" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D32" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H32" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>59990</v>
+      </c>
+      <c r="O32" t="str">
+        <v>2016-07-04</v>
+      </c>
+      <c r="P32" t="str">
+        <v>2037-12-28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>M032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Girard Sarah</v>
+      </c>
+      <c r="C33" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D33" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G33" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H33" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I33" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>60723</v>
+      </c>
+      <c r="O33" t="str">
+        <v>2017-08-05</v>
+      </c>
+      <c r="P33" t="str">
+        <v>2039-01-28</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>M033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Bernard Nadia</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G34" t="str">
+        <v>France</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>61456</v>
+      </c>
+      <c r="O34" t="str">
+        <v>2018-09-06</v>
+      </c>
+      <c r="P34" t="str">
+        <v>2041-02-28</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>M034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Alvarez Marc</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>62189</v>
+      </c>
+      <c r="O35" t="str">
+        <v>2019-10-07</v>
+      </c>
+      <c r="P35" t="str">
+        <v>2043-03-28</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>M035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Dahl Elena</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>62922</v>
+      </c>
+      <c r="O36" t="str">
+        <v>2020-11-08</v>
+      </c>
+      <c r="P36" t="str">
+        <v>2045-04-28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>M036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Vasseur Thomas</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G37" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>63655</v>
+      </c>
+      <c r="O37" t="str">
+        <v>2021-12-09</v>
+      </c>
+      <c r="P37" t="str">
+        <v>2047-05-28</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>M037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Blanc Claire</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G38" t="str">
+        <v>France</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>64388</v>
+      </c>
+      <c r="O38" t="str">
+        <v>2022-01-10</v>
+      </c>
+      <c r="P38" t="str">
+        <v>2049-06-28</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>M038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Nystrom Julien</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>65121</v>
+      </c>
+      <c r="O39" t="str">
+        <v>2023-02-11</v>
+      </c>
+      <c r="P39" t="str">
+        <v>2051-07-28</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>M039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Keller Henrik</v>
+      </c>
+      <c r="C40" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D40" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H40" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>65854</v>
+      </c>
+      <c r="O40" t="str">
+        <v>2024-03-12</v>
+      </c>
+      <c r="P40" t="str">
+        <v>2053-08-28</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>M040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Lambert Ines</v>
+      </c>
+      <c r="C41" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D41" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G41" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H41" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I41" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M41">
+        <v>1</v>
+      </c>
+      <c r="N41">
+        <v>66587</v>
+      </c>
+      <c r="O41" t="str">
+        <v>2012-04-13</v>
+      </c>
+      <c r="P41" t="str">
+        <v>2042-09-28</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>M041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Petit Emma</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G42" t="str">
+        <v>France</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>67320</v>
+      </c>
+      <c r="O42" t="str">
+        <v>2013-05-14</v>
+      </c>
+      <c r="P42" t="str">
+        <v>2044-10-28</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>M042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Roy Louis</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>68053</v>
+      </c>
+      <c r="O43" t="str">
+        <v>2014-06-15</v>
+      </c>
+      <c r="P43" t="str">
+        <v>2046-11-28</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>M043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Moreau Camille</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>68786</v>
+      </c>
+      <c r="O44" t="str">
+        <v>2015-07-16</v>
+      </c>
+      <c r="P44" t="str">
+        <v>2048-12-28</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>M044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Klein Antoine</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G45" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>69519</v>
+      </c>
+      <c r="O45" t="str">
+        <v>2016-08-17</v>
+      </c>
+      <c r="P45" t="str">
+        <v>2050-01-28</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>M045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Fontaine Julie</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G46" t="str">
+        <v>France</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>70252</v>
+      </c>
+      <c r="O46" t="str">
+        <v>2017-09-18</v>
+      </c>
+      <c r="P46" t="str">
+        <v>2052-02-28</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>M046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Weber Hans</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>70985</v>
+      </c>
+      <c r="O47" t="str">
+        <v>2018-10-19</v>
+      </c>
+      <c r="P47" t="str">
+        <v>2039-03-28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>M047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Ruiz Léa</v>
+      </c>
+      <c r="C48" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D48" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H48" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>71718</v>
+      </c>
+      <c r="O48" t="str">
+        <v>2019-11-20</v>
+      </c>
+      <c r="P48" t="str">
+        <v>2041-04-28</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>M048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Diaz Paul</v>
+      </c>
+      <c r="C49" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D49" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G49" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H49" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I49" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>72451</v>
+      </c>
+      <c r="O49" t="str">
+        <v>2020-12-21</v>
+      </c>
+      <c r="P49" t="str">
+        <v>2043-05-28</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>M049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Cole Sofia</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G50" t="str">
+        <v>France</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+      <c r="N50">
+        <v>73184</v>
+      </c>
+      <c r="O50" t="str">
+        <v>2021-01-22</v>
+      </c>
+      <c r="P50" t="str">
+        <v>2045-06-28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>M050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Bennett Mateo</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>73917</v>
+      </c>
+      <c r="O51" t="str">
+        <v>2022-02-23</v>
+      </c>
+      <c r="P51" t="str">
+        <v>2047-07-28</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>M051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Girard Ryan</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>74650</v>
+      </c>
+      <c r="O52" t="str">
+        <v>2023-03-24</v>
+      </c>
+      <c r="P52" t="str">
+        <v>2049-08-28</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>M052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Bernard Sarah</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G53" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M53">
+        <v>1</v>
+      </c>
+      <c r="N53">
+        <v>75383</v>
+      </c>
+      <c r="O53" t="str">
+        <v>2024-04-25</v>
+      </c>
+      <c r="P53" t="str">
+        <v>2051-09-28</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>M053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Alvarez Nadia</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G54" t="str">
+        <v>France</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>76116</v>
+      </c>
+      <c r="O54" t="str">
+        <v>2012-05-26</v>
+      </c>
+      <c r="P54" t="str">
+        <v>2040-10-28</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>M054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Dahl Marc</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>76849</v>
+      </c>
+      <c r="O55" t="str">
+        <v>2013-06-27</v>
+      </c>
+      <c r="P55" t="str">
+        <v>2042-11-28</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>M055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Vasseur Elena</v>
+      </c>
+      <c r="C56" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D56" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H56" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M56">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>77582</v>
+      </c>
+      <c r="O56" t="str">
+        <v>2014-07-01</v>
+      </c>
+      <c r="P56" t="str">
+        <v>2044-12-28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>M056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Blanc Thomas</v>
+      </c>
+      <c r="C57" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D57" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G57" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H57" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I57" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M57">
+        <v>1</v>
+      </c>
+      <c r="N57">
+        <v>78315</v>
+      </c>
+      <c r="O57" t="str">
+        <v>2015-08-02</v>
+      </c>
+      <c r="P57" t="str">
+        <v>2046-01-28</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>M057</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Nystrom Claire</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G58" t="str">
+        <v>France</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>79048</v>
+      </c>
+      <c r="O58" t="str">
+        <v>2016-09-03</v>
+      </c>
+      <c r="P58" t="str">
+        <v>2048-02-28</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>M058</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Keller Julien</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K59" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L59" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M59">
+        <v>1</v>
+      </c>
+      <c r="N59">
+        <v>79781</v>
+      </c>
+      <c r="O59" t="str">
+        <v>2017-10-04</v>
+      </c>
+      <c r="P59" t="str">
+        <v>2050-03-28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>M059</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Lambert Henrik</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K60" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L60" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>38514</v>
+      </c>
+      <c r="O60" t="str">
+        <v>2018-11-05</v>
+      </c>
+      <c r="P60" t="str">
+        <v>2052-04-28</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>M060</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Garnier Ines</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G61" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L61" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M61">
+        <v>1</v>
+      </c>
+      <c r="N61">
+        <v>39247</v>
+      </c>
+      <c r="O61" t="str">
+        <v>2019-12-06</v>
+      </c>
+      <c r="P61" t="str">
+        <v>2054-05-28</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>M061</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Roy Emma</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G62" t="str">
+        <v>France</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J62" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K62" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L62" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M62">
+        <v>1</v>
+      </c>
+      <c r="N62">
+        <v>39980</v>
+      </c>
+      <c r="O62" t="str">
+        <v>2020-01-07</v>
+      </c>
+      <c r="P62" t="str">
+        <v>2041-06-28</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>M062</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Moreau Louis</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J63" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+      <c r="N63">
+        <v>40713</v>
+      </c>
+      <c r="O63" t="str">
+        <v>2021-02-08</v>
+      </c>
+      <c r="P63" t="str">
+        <v>2043-07-28</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>M063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Klein Camille</v>
+      </c>
+      <c r="C64" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D64" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H64" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="N64">
+        <v>41446</v>
+      </c>
+      <c r="O64" t="str">
+        <v>2022-03-09</v>
+      </c>
+      <c r="P64" t="str">
+        <v>2045-08-28</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>M064</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Fontaine Antoine</v>
+      </c>
+      <c r="C65" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D65" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G65" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H65" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I65" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+      <c r="N65">
+        <v>42179</v>
+      </c>
+      <c r="O65" t="str">
+        <v>2023-04-10</v>
+      </c>
+      <c r="P65" t="str">
+        <v>2047-09-28</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>M065</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Weber Julie</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G66" t="str">
+        <v>France</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+      <c r="N66">
+        <v>42912</v>
+      </c>
+      <c r="O66" t="str">
+        <v>2024-05-11</v>
+      </c>
+      <c r="P66" t="str">
+        <v>2049-10-28</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>M066</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Ruiz Hans</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G67" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="N67">
+        <v>43645</v>
+      </c>
+      <c r="O67" t="str">
+        <v>2012-06-12</v>
+      </c>
+      <c r="P67" t="str">
+        <v>2038-11-28</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>M067</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Diaz Léa</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J68" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>44378</v>
+      </c>
+      <c r="O68" t="str">
+        <v>2013-07-13</v>
+      </c>
+      <c r="P68" t="str">
+        <v>2040-12-28</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>M068</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Cole Paul</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G69" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J69" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+      <c r="N69">
+        <v>45111</v>
+      </c>
+      <c r="O69" t="str">
+        <v>2014-08-14</v>
+      </c>
+      <c r="P69" t="str">
+        <v>2042-01-28</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>M069</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Bennett Sofia</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G70" t="str">
+        <v>France</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J70" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>45844</v>
+      </c>
+      <c r="O70" t="str">
+        <v>2015-09-15</v>
+      </c>
+      <c r="P70" t="str">
+        <v>2044-02-28</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>M070</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Girard Mateo</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G71" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+      <c r="N71">
+        <v>46577</v>
+      </c>
+      <c r="O71" t="str">
+        <v>2016-10-16</v>
+      </c>
+      <c r="P71" t="str">
+        <v>2046-03-28</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>M071</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Bernard Ryan</v>
+      </c>
+      <c r="C72" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D72" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G72" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H72" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>47310</v>
+      </c>
+      <c r="O72" t="str">
+        <v>2017-11-17</v>
+      </c>
+      <c r="P72" t="str">
+        <v>2048-04-28</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>M072</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Alvarez Sarah</v>
+      </c>
+      <c r="C73" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D73" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G73" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H73" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I73" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="N73">
+        <v>48043</v>
+      </c>
+      <c r="O73" t="str">
+        <v>2018-12-18</v>
+      </c>
+      <c r="P73" t="str">
+        <v>2050-05-28</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>M073</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Dahl Nadia</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G74" t="str">
+        <v>France</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J74" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+      <c r="N74">
+        <v>48776</v>
+      </c>
+      <c r="O74" t="str">
+        <v>2019-01-19</v>
+      </c>
+      <c r="P74" t="str">
+        <v>2052-06-28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>M074</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Vasseur Marc</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G75" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J75" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>49509</v>
+      </c>
+      <c r="O75" t="str">
+        <v>2020-02-20</v>
+      </c>
+      <c r="P75" t="str">
+        <v>2054-07-28</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>M075</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Blanc Elena</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G76" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J76" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>50242</v>
+      </c>
+      <c r="O76" t="str">
+        <v>2021-03-21</v>
+      </c>
+      <c r="P76" t="str">
+        <v>2056-08-28</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>M076</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Nystrom Thomas</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G77" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J77" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>50975</v>
+      </c>
+      <c r="O77" t="str">
+        <v>2022-04-22</v>
+      </c>
+      <c r="P77" t="str">
+        <v>2043-09-28</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>M077</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Keller Claire</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G78" t="str">
+        <v>France</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>51708</v>
+      </c>
+      <c r="O78" t="str">
+        <v>2023-05-23</v>
+      </c>
+      <c r="P78" t="str">
+        <v>2045-10-28</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>M078</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Lambert Julien</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J79" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>52441</v>
+      </c>
+      <c r="O79" t="str">
+        <v>2024-06-24</v>
+      </c>
+      <c r="P79" t="str">
+        <v>2047-11-28</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>M079</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Garnier Henrik</v>
+      </c>
+      <c r="C80" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D80" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G80" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H80" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80">
+        <v>53174</v>
+      </c>
+      <c r="O80" t="str">
+        <v>2012-07-25</v>
+      </c>
+      <c r="P80" t="str">
+        <v>2036-12-28</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>M080</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Petit Ines</v>
+      </c>
+      <c r="C81" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D81" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G81" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H81" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I81" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>53907</v>
+      </c>
+      <c r="O81" t="str">
+        <v>2013-08-26</v>
+      </c>
+      <c r="P81" t="str">
+        <v>2038-01-28</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>M081</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Moreau Emma</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G82" t="str">
+        <v>France</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>54640</v>
+      </c>
+      <c r="O82" t="str">
+        <v>2014-09-27</v>
+      </c>
+      <c r="P82" t="str">
+        <v>2040-02-28</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>M082</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Klein Louis</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G83" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>55373</v>
+      </c>
+      <c r="O83" t="str">
+        <v>2015-10-01</v>
+      </c>
+      <c r="P83" t="str">
+        <v>2042-03-28</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>M083</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Fontaine Camille</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G84" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J84" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84">
+        <v>56106</v>
+      </c>
+      <c r="O84" t="str">
+        <v>2016-11-02</v>
+      </c>
+      <c r="P84" t="str">
+        <v>2044-04-28</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>M084</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Weber Antoine</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G85" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J85" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>56839</v>
+      </c>
+      <c r="O85" t="str">
+        <v>2017-12-03</v>
+      </c>
+      <c r="P85" t="str">
+        <v>2046-05-28</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>M085</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Ruiz Julie</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G86" t="str">
+        <v>France</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J86" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K86" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M86">
+        <v>1</v>
+      </c>
+      <c r="N86">
+        <v>57572</v>
+      </c>
+      <c r="O86" t="str">
+        <v>2018-01-04</v>
+      </c>
+      <c r="P86" t="str">
+        <v>2048-06-28</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>M086</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Diaz Hans</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G87" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J87" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87">
+        <v>58305</v>
+      </c>
+      <c r="O87" t="str">
+        <v>2019-02-05</v>
+      </c>
+      <c r="P87" t="str">
+        <v>2050-07-28</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>M087</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Cole Léa</v>
+      </c>
+      <c r="C88" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D88" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G88" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H88" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J88" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>59038</v>
+      </c>
+      <c r="O88" t="str">
+        <v>2020-03-06</v>
+      </c>
+      <c r="P88" t="str">
+        <v>2052-08-28</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>M088</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Bennett Paul</v>
+      </c>
+      <c r="C89" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D89" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G89" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H89" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I89" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J89" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>59771</v>
+      </c>
+      <c r="O89" t="str">
+        <v>2021-04-07</v>
+      </c>
+      <c r="P89" t="str">
+        <v>2054-09-28</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>M089</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Girard Sofia</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G90" t="str">
+        <v>France</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M90">
+        <v>1</v>
+      </c>
+      <c r="N90">
+        <v>60504</v>
+      </c>
+      <c r="O90" t="str">
+        <v>2022-05-08</v>
+      </c>
+      <c r="P90" t="str">
+        <v>2056-10-28</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>M090</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Bernard Mateo</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G91" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J91" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M91">
+        <v>1</v>
+      </c>
+      <c r="N91">
+        <v>61237</v>
+      </c>
+      <c r="O91" t="str">
+        <v>2023-06-09</v>
+      </c>
+      <c r="P91" t="str">
+        <v>2058-11-28</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>M091</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Alvarez Ryan</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G92" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J92" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K92" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92">
+        <v>61970</v>
+      </c>
+      <c r="O92" t="str">
+        <v>2024-07-10</v>
+      </c>
+      <c r="P92" t="str">
+        <v>2045-12-28</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>M092</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Dahl Sarah</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G93" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J93" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K93" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>62703</v>
+      </c>
+      <c r="O93" t="str">
+        <v>2012-08-11</v>
+      </c>
+      <c r="P93" t="str">
+        <v>2034-01-28</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>M093</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Vasseur Nadia</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G94" t="str">
+        <v>France</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Ventes terrain</v>
+      </c>
+      <c r="J94" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>63436</v>
+      </c>
+      <c r="O94" t="str">
+        <v>2013-09-12</v>
+      </c>
+      <c r="P94" t="str">
+        <v>2036-02-28</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>M094</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Blanc Marc</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G95" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Entrepôts</v>
+      </c>
+      <c r="J95" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>64169</v>
+      </c>
+      <c r="O95" t="str">
+        <v>2014-10-13</v>
+      </c>
+      <c r="P95" t="str">
+        <v>2038-03-28</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>M095</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Nystrom Elena</v>
+      </c>
+      <c r="C96" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D96" t="str">
+        <v>IT</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G96" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H96" t="str">
+        <v>IT</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Support SI</v>
+      </c>
+      <c r="J96" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>64902</v>
+      </c>
+      <c r="O96" t="str">
+        <v>2015-11-14</v>
+      </c>
+      <c r="P96" t="str">
+        <v>2040-04-28</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>M096</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Keller Thomas</v>
+      </c>
+      <c r="C97" t="str">
+        <v>RH</v>
+      </c>
+      <c r="D97" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G97" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H97" t="str">
+        <v>HR</v>
+      </c>
+      <c r="I97" t="str">
+        <v>RH Généraliste</v>
+      </c>
+      <c r="J97" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>65635</v>
+      </c>
+      <c r="O97" t="str">
+        <v>2016-12-15</v>
+      </c>
+      <c r="P97" t="str">
+        <v>2042-05-28</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>M097</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Lambert Claire</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G98" t="str">
+        <v>France</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Achats directs</v>
+      </c>
+      <c r="J98" t="str">
+        <v>Acme France</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>66368</v>
+      </c>
+      <c r="O98" t="str">
+        <v>2017-01-16</v>
+      </c>
+      <c r="P98" t="str">
+        <v>2044-06-28</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>M098</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Garnier Julien</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Production</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Opérations</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G99" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Ligne de production</v>
+      </c>
+      <c r="J99" t="str">
+        <v>Acme Deutschland</v>
+      </c>
+      <c r="K99" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Local</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>67101</v>
+      </c>
+      <c r="O99" t="str">
+        <v>2018-02-17</v>
+      </c>
+      <c r="P99" t="str">
+        <v>2046-07-28</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>M099</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Petit Henrik</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G100" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Marketing Central</v>
+      </c>
+      <c r="J100" t="str">
+        <v>Acme Iberia</v>
+      </c>
+      <c r="K100" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Régional</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>67834</v>
+      </c>
+      <c r="O100" t="str">
+        <v>2019-03-18</v>
+      </c>
+      <c r="P100" t="str">
+        <v>2048-08-28</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>M100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Roy Ines</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="G101" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="J101" t="str">
+        <v>Acme USA</v>
+      </c>
+      <c r="K101" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Global</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101">
+        <v>68567</v>
+      </c>
+      <c r="O101" t="str">
+        <v>2020-04-19</v>
+      </c>
+      <c r="P101" t="str">
+        <v>2050-09-28</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P101"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1125,10 +5525,10 @@
         <v>MV-001</v>
       </c>
       <c r="B2" t="str">
-        <v>M002</v>
+        <v>M001</v>
       </c>
       <c r="C2" t="str">
-        <v>Garnier Louis</v>
+        <v>Lambert Emma</v>
       </c>
       <c r="D2" t="str">
         <v>Suppression</v>
@@ -1152,7 +5552,7 @@
         <v>AC-001</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-07-01</v>
+        <v>2026-01-15</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -1164,19 +5564,19 @@
         <v>Non</v>
       </c>
       <c r="O2" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="P2">
-        <v>-52000</v>
+        <v>-38000</v>
       </c>
       <c r="Q2">
-        <v>52000</v>
+        <v>38000</v>
       </c>
       <c r="R2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="S2" t="str">
-        <v>Poste supprimé suite au regroupement fournisseurs.</v>
+        <v>Mouvement de démo généré (suppression, lié à AC-001).</v>
       </c>
     </row>
     <row r="3">
@@ -1184,10 +5584,10 @@
         <v>MV-002</v>
       </c>
       <c r="B3" t="str">
-        <v>M004</v>
+        <v>M006</v>
       </c>
       <c r="C3" t="str">
-        <v>Roy Antoine</v>
+        <v>Klein Hans</v>
       </c>
       <c r="D3" t="str">
         <v>Redéploiement</v>
@@ -1196,31 +5596,31 @@
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>Production</v>
+        <v>Logistique</v>
       </c>
       <c r="G3" t="str">
-        <v>Maintenance</v>
+        <v>Marketing</v>
       </c>
       <c r="H3" t="str">
-        <v>France</v>
+        <v>Germany</v>
       </c>
       <c r="I3" t="str">
         <v>Sophie Dubois</v>
       </c>
       <c r="J3" t="str">
-        <v>AC-002</v>
+        <v>AC-004</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-06-01</v>
+        <v>2026-02-15</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-06-01</v>
+        <v/>
       </c>
       <c r="M3" t="str">
-        <v>Réalisé</v>
+        <v>En cours</v>
       </c>
       <c r="N3" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="O3" t="str">
         <v>Non</v>
@@ -1232,10 +5632,10 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="S3" t="str">
-        <v>Reclassé sur l'équipe maintenance préventive.</v>
+        <v>Mouvement de démo généré (redéploiement, lié à AC-004).</v>
       </c>
     </row>
     <row r="4">
@@ -1243,10 +5643,10 @@
         <v>MV-003</v>
       </c>
       <c r="B4" t="str">
-        <v>M006</v>
+        <v>M011</v>
       </c>
       <c r="C4" t="str">
-        <v>Klein Hans</v>
+        <v>Cole Ryan</v>
       </c>
       <c r="D4" t="str">
         <v>Reconversion</v>
@@ -1258,31 +5658,31 @@
         <v>Marketing</v>
       </c>
       <c r="G4" t="str">
-        <v>Marketing Central</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Germany</v>
+        <v>Spain</v>
       </c>
       <c r="I4" t="str">
         <v>Claire Moreau</v>
       </c>
       <c r="J4" t="str">
-        <v>AC-004</v>
+        <v>AC-007</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-08-01</v>
+        <v>2026-03-15</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>2026-03-15</v>
       </c>
       <c r="M4" t="str">
-        <v>Planifié</v>
+        <v>Réalisé</v>
       </c>
       <c r="N4" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O4" t="str">
         <v>Non</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Oui</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1291,10 +5691,10 @@
         <v>0</v>
       </c>
       <c r="R4">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="S4" t="str">
-        <v>Formation de reconversion suite à la fusion des équipes.</v>
+        <v>Mouvement de démo généré (reconversion, lié à AC-007).</v>
       </c>
     </row>
     <row r="5">
@@ -1302,13 +5702,13 @@
         <v>MV-004</v>
       </c>
       <c r="B5" t="str">
-        <v>M008</v>
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>Weber Paul</v>
+        <v>Poste à recruter (AC-010)</v>
       </c>
       <c r="D5" t="str">
-        <v>Suppression</v>
+        <v>Recrutement</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1320,16 +5720,16 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Germany</v>
+        <v>USA</v>
       </c>
       <c r="I5" t="str">
         <v>Claire Moreau</v>
       </c>
       <c r="J5" t="str">
-        <v>AC-003</v>
+        <v>AC-010</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-10-01</v>
+        <v>2026-04-15</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -1341,19 +5741,19 @@
         <v>Non</v>
       </c>
       <c r="O5" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="P5">
-        <v>-56000</v>
+        <v>45000</v>
       </c>
       <c r="Q5">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="S5" t="str">
-        <v>Automatisation du back-office comptable.</v>
+        <v>Mouvement de démo généré (recrutement, lié à AC-010).</v>
       </c>
     </row>
     <row r="6">
@@ -1361,40 +5761,40 @@
         <v>MV-005</v>
       </c>
       <c r="B6" t="str">
-        <v>M012</v>
+        <v>M021</v>
       </c>
       <c r="C6" t="str">
-        <v>Bennett Sarah</v>
+        <v>Garnier Emma</v>
       </c>
       <c r="D6" t="str">
-        <v>Redéploiement</v>
+        <v>Suppression</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>Logistique</v>
+        <v>Ventes</v>
       </c>
       <c r="G6" t="str">
-        <v>Entrepôts</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>USA</v>
+        <v>France</v>
       </c>
       <c r="I6" t="str">
         <v>Sophie Dubois</v>
       </c>
       <c r="J6" t="str">
-        <v>AC-006</v>
+        <v>AC-013</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-09-01</v>
+        <v>2026-05-15</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>Planifié</v>
+        <v>En cours</v>
       </c>
       <c r="N6" t="str">
         <v>Non</v>
@@ -1403,16 +5803,16 @@
         <v>Non</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>-52660</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>52660</v>
       </c>
       <c r="R6">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="S6" t="str">
-        <v>Réaffectée sur le site consolidé.</v>
+        <v>Mouvement de démo généré (suppression, lié à AC-013).</v>
       </c>
     </row>
     <row r="7">
@@ -1420,13 +5820,13 @@
         <v>MV-006</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>M026</v>
       </c>
       <c r="C7" t="str">
-        <v>Ingénieur Qualité (à recruter)</v>
+        <v>Fontaine Hans</v>
       </c>
       <c r="D7" t="str">
-        <v>Recrutement</v>
+        <v>Redéploiement</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1435,48 +5835,874 @@
         <v>Production</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>IT</v>
       </c>
       <c r="H7" t="str">
-        <v>France</v>
+        <v>Germany</v>
       </c>
       <c r="I7" t="str">
         <v>Sophie Dubois</v>
       </c>
       <c r="J7" t="str">
-        <v>AC-007</v>
+        <v>AC-016</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-05-01</v>
+        <v>2026-06-15</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>2026-06-15</v>
       </c>
       <c r="M7" t="str">
-        <v>Planifié</v>
+        <v>Réalisé</v>
       </c>
       <c r="N7" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="O7" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="P7">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>4000</v>
+        <v>9500</v>
       </c>
       <c r="S7" t="str">
-        <v>Recrutement lié au programme qualité production.</v>
+        <v>Mouvement de démo généré (redéploiement, lié à AC-016).</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>MV-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>M031</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Bennett Ryan</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Reconversion</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="str">
+        <v>IT</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J8" t="str">
+        <v>AC-019</v>
+      </c>
+      <c r="K8" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>2000</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Mouvement de démo généré (reconversion, lié à AC-019).</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>MV-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>Poste à recruter (AC-022)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Recrutement</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>RH</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J9" t="str">
+        <v>AC-022</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-08-15</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P9">
+        <v>45000</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>3500</v>
+      </c>
+      <c r="S9" t="str">
+        <v>Mouvement de démo généré (recrutement, lié à AC-022).</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>MV-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>M041</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Petit Emma</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Suppression</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>France</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J10" t="str">
+        <v>AC-025</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P10">
+        <v>-67320</v>
+      </c>
+      <c r="Q10">
+        <v>67320</v>
+      </c>
+      <c r="R10">
+        <v>5000</v>
+      </c>
+      <c r="S10" t="str">
+        <v>Mouvement de démo généré (suppression, lié à AC-025).</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>MV-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>M046</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Weber Hans</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Redéploiement</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J11" t="str">
+        <v>AC-028</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N11" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>6500</v>
+      </c>
+      <c r="S11" t="str">
+        <v>Mouvement de démo généré (redéploiement, lié à AC-028).</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>MV-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>M051</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Girard Ryan</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Reconversion</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J12" t="str">
+        <v>AC-001</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2026-11-15</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="N12" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>8000</v>
+      </c>
+      <c r="S12" t="str">
+        <v>Mouvement de démo généré (reconversion, lié à AC-001).</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MV-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>Poste à recruter (AC-004)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Recrutement</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J13" t="str">
+        <v>AC-004</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N13" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P13">
+        <v>45000</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>9500</v>
+      </c>
+      <c r="S13" t="str">
+        <v>Mouvement de démo généré (recrutement, lié à AC-004).</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>MV-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>M061</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Roy Emma</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Suppression</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>France</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J14" t="str">
+        <v>AC-007</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2026-01-15</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N14" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P14">
+        <v>-39980</v>
+      </c>
+      <c r="Q14">
+        <v>39980</v>
+      </c>
+      <c r="R14">
+        <v>2000</v>
+      </c>
+      <c r="S14" t="str">
+        <v>Mouvement de démo généré (suppression, lié à AC-007).</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>MV-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>M066</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Ruiz Hans</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Redéploiement</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Production</v>
+      </c>
+      <c r="G15" t="str">
+        <v>IT</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J15" t="str">
+        <v>AC-010</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="N15" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>3500</v>
+      </c>
+      <c r="S15" t="str">
+        <v>Mouvement de démo généré (redéploiement, lié à AC-010).</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>MV-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>M071</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Bernard Ryan</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Reconversion</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="str">
+        <v>IT</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J16" t="str">
+        <v>AC-013</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="L16" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N16" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O16" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>5000</v>
+      </c>
+      <c r="S16" t="str">
+        <v>Mouvement de démo généré (reconversion, lié à AC-013).</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>MV-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v>Poste à recruter (AC-016)</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Recrutement</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="str">
+        <v>RH</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J17" t="str">
+        <v>AC-016</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N17" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O17" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="P17">
+        <v>45000</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>6500</v>
+      </c>
+      <c r="S17" t="str">
+        <v>Mouvement de démo généré (recrutement, lié à AC-016).</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>MV-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>M081</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Moreau Emma</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Suppression</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>France</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J18" t="str">
+        <v>AC-019</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="N18" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O18" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P18">
+        <v>-54640</v>
+      </c>
+      <c r="Q18">
+        <v>54640</v>
+      </c>
+      <c r="R18">
+        <v>8000</v>
+      </c>
+      <c r="S18" t="str">
+        <v>Mouvement de démo généré (suppression, lié à AC-019).</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>MV-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>M086</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Diaz Hans</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Redéploiement</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J19" t="str">
+        <v>AC-022</v>
+      </c>
+      <c r="K19" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="L19" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N19" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O19" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>9500</v>
+      </c>
+      <c r="S19" t="str">
+        <v>Mouvement de démo généré (redéploiement, lié à AC-022).</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>MV-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>M091</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Alvarez Ryan</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Reconversion</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J20" t="str">
+        <v>AC-025</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N20" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>2000</v>
+      </c>
+      <c r="S20" t="str">
+        <v>Mouvement de démo généré (reconversion, lié à AC-025).</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>MV-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>Poste à recruter (AC-028)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Recrutement</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J21" t="str">
+        <v>AC-028</v>
+      </c>
+      <c r="K21" t="str">
+        <v>2026-08-15</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="N21" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P21">
+        <v>45000</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>3500</v>
+      </c>
+      <c r="S21" t="str">
+        <v>Mouvement de démo généré (recrutement, lié à AC-028).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/demo/base_etp_demo.xlsx
+++ b/demo/base_etp_demo.xlsx
@@ -5531,7 +5531,7 @@
         <v>Lambert Emma</v>
       </c>
       <c r="D2" t="str">
-        <v>Suppression</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -5576,7 +5576,7 @@
         <v>2000</v>
       </c>
       <c r="S2" t="str">
-        <v>Mouvement de démo généré (suppression, lié à AC-001).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-001).</v>
       </c>
     </row>
     <row r="3">
@@ -5590,7 +5590,7 @@
         <v>Klein Hans</v>
       </c>
       <c r="D3" t="str">
-        <v>Redéploiement</v>
+        <v>Transfert entrant</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -5617,7 +5617,7 @@
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>En cours</v>
+        <v>À faire</v>
       </c>
       <c r="N3" t="str">
         <v>Non</v>
@@ -5635,7 +5635,7 @@
         <v>3500</v>
       </c>
       <c r="S3" t="str">
-        <v>Mouvement de démo généré (redéploiement, lié à AC-004).</v>
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-004).</v>
       </c>
     </row>
     <row r="4">
@@ -5649,7 +5649,7 @@
         <v>Cole Ryan</v>
       </c>
       <c r="D4" t="str">
-        <v>Reconversion</v>
+        <v>Transfert sortant</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -5694,7 +5694,7 @@
         <v>5000</v>
       </c>
       <c r="S4" t="str">
-        <v>Mouvement de démo généré (reconversion, lié à AC-007).</v>
+        <v>Mouvement de démo généré (transfert sortant, lié à AC-007).</v>
       </c>
     </row>
     <row r="5">
@@ -5767,7 +5767,7 @@
         <v>Garnier Emma</v>
       </c>
       <c r="D6" t="str">
-        <v>Suppression</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -5794,7 +5794,7 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>En cours</v>
+        <v>À faire</v>
       </c>
       <c r="N6" t="str">
         <v>Non</v>
@@ -5812,7 +5812,7 @@
         <v>8000</v>
       </c>
       <c r="S6" t="str">
-        <v>Mouvement de démo généré (suppression, lié à AC-013).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-013).</v>
       </c>
     </row>
     <row r="7">
@@ -5826,7 +5826,7 @@
         <v>Fontaine Hans</v>
       </c>
       <c r="D7" t="str">
-        <v>Redéploiement</v>
+        <v>Transfert entrant</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -5871,7 +5871,7 @@
         <v>9500</v>
       </c>
       <c r="S7" t="str">
-        <v>Mouvement de démo généré (redéploiement, lié à AC-016).</v>
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-016).</v>
       </c>
     </row>
     <row r="8">
@@ -5885,7 +5885,7 @@
         <v>Bennett Ryan</v>
       </c>
       <c r="D8" t="str">
-        <v>Reconversion</v>
+        <v>Transfert sortant</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -5930,7 +5930,7 @@
         <v>2000</v>
       </c>
       <c r="S8" t="str">
-        <v>Mouvement de démo généré (reconversion, lié à AC-019).</v>
+        <v>Mouvement de démo généré (transfert sortant, lié à AC-019).</v>
       </c>
     </row>
     <row r="9">
@@ -5971,7 +5971,7 @@
         <v/>
       </c>
       <c r="M9" t="str">
-        <v>En cours</v>
+        <v>À faire</v>
       </c>
       <c r="N9" t="str">
         <v>Non</v>
@@ -6003,7 +6003,7 @@
         <v>Petit Emma</v>
       </c>
       <c r="D10" t="str">
-        <v>Suppression</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -6048,7 +6048,7 @@
         <v>5000</v>
       </c>
       <c r="S10" t="str">
-        <v>Mouvement de démo généré (suppression, lié à AC-025).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-025).</v>
       </c>
     </row>
     <row r="11">
@@ -6062,7 +6062,7 @@
         <v>Weber Hans</v>
       </c>
       <c r="D11" t="str">
-        <v>Redéploiement</v>
+        <v>Transfert entrant</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -6107,7 +6107,7 @@
         <v>6500</v>
       </c>
       <c r="S11" t="str">
-        <v>Mouvement de démo généré (redéploiement, lié à AC-028).</v>
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-028).</v>
       </c>
     </row>
     <row r="12">
@@ -6121,7 +6121,7 @@
         <v>Girard Ryan</v>
       </c>
       <c r="D12" t="str">
-        <v>Reconversion</v>
+        <v>Transfert sortant</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -6148,7 +6148,7 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>En cours</v>
+        <v>À faire</v>
       </c>
       <c r="N12" t="str">
         <v>Non</v>
@@ -6166,7 +6166,7 @@
         <v>8000</v>
       </c>
       <c r="S12" t="str">
-        <v>Mouvement de démo généré (reconversion, lié à AC-001).</v>
+        <v>Mouvement de démo généré (transfert sortant, lié à AC-001).</v>
       </c>
     </row>
     <row r="13">
@@ -6239,7 +6239,7 @@
         <v>Roy Emma</v>
       </c>
       <c r="D14" t="str">
-        <v>Suppression</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -6284,7 +6284,7 @@
         <v>2000</v>
       </c>
       <c r="S14" t="str">
-        <v>Mouvement de démo généré (suppression, lié à AC-007).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-007).</v>
       </c>
     </row>
     <row r="15">
@@ -6298,7 +6298,7 @@
         <v>Ruiz Hans</v>
       </c>
       <c r="D15" t="str">
-        <v>Redéploiement</v>
+        <v>Transfert entrant</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -6325,7 +6325,7 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>En cours</v>
+        <v>À faire</v>
       </c>
       <c r="N15" t="str">
         <v>Non</v>
@@ -6343,7 +6343,7 @@
         <v>3500</v>
       </c>
       <c r="S15" t="str">
-        <v>Mouvement de démo généré (redéploiement, lié à AC-010).</v>
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-010).</v>
       </c>
     </row>
     <row r="16">
@@ -6357,7 +6357,7 @@
         <v>Bernard Ryan</v>
       </c>
       <c r="D16" t="str">
-        <v>Reconversion</v>
+        <v>Transfert sortant</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -6402,7 +6402,7 @@
         <v>5000</v>
       </c>
       <c r="S16" t="str">
-        <v>Mouvement de démo généré (reconversion, lié à AC-013).</v>
+        <v>Mouvement de démo généré (transfert sortant, lié à AC-013).</v>
       </c>
     </row>
     <row r="17">
@@ -6475,7 +6475,7 @@
         <v>Moreau Emma</v>
       </c>
       <c r="D18" t="str">
-        <v>Suppression</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6502,7 +6502,7 @@
         <v/>
       </c>
       <c r="M18" t="str">
-        <v>En cours</v>
+        <v>À faire</v>
       </c>
       <c r="N18" t="str">
         <v>Non</v>
@@ -6520,7 +6520,7 @@
         <v>8000</v>
       </c>
       <c r="S18" t="str">
-        <v>Mouvement de démo généré (suppression, lié à AC-019).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-019).</v>
       </c>
     </row>
     <row r="19">
@@ -6534,7 +6534,7 @@
         <v>Diaz Hans</v>
       </c>
       <c r="D19" t="str">
-        <v>Redéploiement</v>
+        <v>Transfert entrant</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -6579,7 +6579,7 @@
         <v>9500</v>
       </c>
       <c r="S19" t="str">
-        <v>Mouvement de démo généré (redéploiement, lié à AC-022).</v>
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-022).</v>
       </c>
     </row>
     <row r="20">
@@ -6593,7 +6593,7 @@
         <v>Alvarez Ryan</v>
       </c>
       <c r="D20" t="str">
-        <v>Reconversion</v>
+        <v>Transfert sortant</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -6638,7 +6638,7 @@
         <v>2000</v>
       </c>
       <c r="S20" t="str">
-        <v>Mouvement de démo généré (reconversion, lié à AC-025).</v>
+        <v>Mouvement de démo généré (transfert sortant, lié à AC-025).</v>
       </c>
     </row>
     <row r="21">
@@ -6679,7 +6679,7 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v>En cours</v>
+        <v>À faire</v>
       </c>
       <c r="N21" t="str">
         <v>Non</v>
